--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -261,6 +261,30 @@
   </si>
   <si>
     <t>造成伤害</t>
+  </si>
+  <si>
+    <t>TaskApplyEffects</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>CatchAreaBox3D</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>0,0,3</t>
+  </si>
+  <si>
+    <t>2,2,5</t>
+  </si>
+  <si>
+    <t>0,0,0</t>
+  </si>
+  <si>
+    <t>256</t>
   </si>
   <si>
     <t>测试时间轴2</t>
@@ -969,7 +993,28 @@
         <v>45</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -977,7 +1022,7 @@
         <v>102</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D11" s="4">
         <v>50</v>
@@ -986,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G11" s="4">
         <v>3</v>
@@ -995,13 +1040,13 @@
         <v>4</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>37</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -1012,13 +1057,13 @@
         <v>50</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>37</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -239,7 +239,7 @@
     <t>TaskDebug</t>
   </si>
   <si>
-    <t>测试135</t>
+    <t>播放攻击音效1</t>
   </si>
   <si>
     <t>特效轨道</t>
@@ -266,7 +266,7 @@
     <t>TaskApplyEffects</t>
   </si>
   <si>
-    <t>1001</t>
+    <t>2002</t>
   </si>
   <si>
     <t>CatchAreaBox3D</t>
@@ -984,10 +984,10 @@
     </row>
     <row r="10">
       <c r="G10" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H10" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>45</v>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\EX_GAS_Config\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8775547E-C4AA-48A8-9FB1-973175D32583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>fangmenglu</author>
   </authors>
   <commentList>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -304,11 +303,68 @@
   <si>
     <t>结尾</t>
   </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>Cue轨道1</t>
+  </si>
+  <si>
+    <t>前摇动画</t>
+  </si>
+  <si>
+    <t>dodge</t>
+  </si>
+  <si>
+    <t>闪避动画</t>
+  </si>
+  <si>
+    <t>dodge_move</t>
+  </si>
+  <si>
+    <t>闪避结束动画</t>
+  </si>
+  <si>
+    <t>dodge_finish</t>
+  </si>
+  <si>
+    <t>功能轨道1</t>
+  </si>
+  <si>
+    <t>闪避Task逻辑</t>
+  </si>
+  <si>
+    <t>TaskDodgeMove</t>
+  </si>
+  <si>
+    <t>功能轨道2</t>
+  </si>
+  <si>
+    <t>执行消耗</t>
+  </si>
+  <si>
+    <t>添加无敌帧</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>CatchSelf</t>
+  </si>
+  <si>
+    <t>功能轨道3</t>
+  </si>
+  <si>
+    <t>执行Cooldown冷却</t>
+  </si>
+  <si>
+    <t>TaskDoCooldown</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="0"/>
   <fonts count="2">
     <font>
@@ -676,23 +732,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y19"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="16.21875" customWidth="1" style="4"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1" style="4"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1" style="4"/>
-    <col min="6" max="6" width="14.44140625" customWidth="1" style="4"/>
-    <col min="7" max="7" width="18.109375" customWidth="1" style="4"/>
-    <col min="8" max="8" width="14.44140625" customWidth="1" style="4"/>
-    <col min="9" max="9" width="16.77734375" customWidth="1" style="4"/>
+    <col min="3" max="3" width="16.25" customWidth="1" style="4"/>
+    <col min="4" max="4" width="14.5" customWidth="1" style="4"/>
+    <col min="5" max="5" width="20.5" customWidth="1" style="4"/>
+    <col min="6" max="6" width="14.5" customWidth="1" style="4"/>
+    <col min="7" max="7" width="18.125" customWidth="1" style="4"/>
+    <col min="8" max="8" width="14.5" customWidth="1" style="4"/>
+    <col min="9" max="9" width="16.75" customWidth="1" style="4"/>
     <col min="10" max="10" width="15" customWidth="1" style="4"/>
-    <col min="11" max="11" width="12.33203125" customWidth="1" style="3"/>
-    <col min="12" max="12" width="14.88671875" customWidth="1" style="3"/>
-    <col min="13" max="13" width="13.6640625" customWidth="1" style="3"/>
-    <col min="14" max="14" width="11.88671875" customWidth="1" style="3"/>
-    <col min="15" max="15" width="14.77734375" customWidth="1" style="3"/>
+    <col min="11" max="11" width="12.375" customWidth="1" style="3"/>
+    <col min="12" max="12" width="14.875" customWidth="1" style="3"/>
+    <col min="13" max="13" width="13.625" customWidth="1" style="3"/>
+    <col min="14" max="14" width="11.875" customWidth="1" style="3"/>
+    <col min="15" max="15" width="14.75" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1066,6 +1122,185 @@
         <v>59</v>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" s="2">
+        <v>103</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="4">
+        <v>25</v>
+      </c>
+      <c r="E13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>5</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="G14" s="4">
+        <v>5</v>
+      </c>
+      <c r="H14" s="4">
+        <v>18</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="G15" s="4">
+        <v>18</v>
+      </c>
+      <c r="H15" s="4">
+        <v>25</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>18</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" s="3">
+        <v>10</v>
+      </c>
+      <c r="L16" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="F17" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="4">
+        <v>5</v>
+      </c>
+      <c r="H17" s="4">
+        <v>5</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="G18" s="4">
+        <v>5</v>
+      </c>
+      <c r="H18" s="4">
+        <v>18</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="F19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="4">
+        <v>5</v>
+      </c>
+      <c r="H19" s="4">
+        <v>5</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="J4:T4"/>
